--- a/Assets/Ressources/Stats/Enemies_stats.xlsx
+++ b/Assets/Ressources/Stats/Enemies_stats.xlsx
@@ -1,25 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4436A88F-7AC2-4F40-B392-56B2E0356D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Terestrial" sheetId="1" r:id="rId1"/>
+    <sheet name="Marine" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>ATK</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +362,2833 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>50</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>INT(B$2 + ($A3 - 1) * ((B$101 - B$2) / 99))</f>
+        <v>302</v>
+      </c>
+      <c r="C3">
+        <f>INT(C$2 + ($A3 - 1) * ((C$101 - C$2) / 99))</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f t="shared" ref="A4:A67" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ref="B4:C67" si="1">INT(B$2 + ($A4 - 1) * ((B$101 - B$2) / 99))</f>
+        <v>554</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="1"/>
+        <v>806</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="1"/>
+        <v>1058</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="1"/>
+        <v>1310</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="1"/>
+        <v>1562</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="1"/>
+        <v>1814</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="1"/>
+        <v>2066</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="1"/>
+        <v>2318</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="1"/>
+        <v>2570</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="1"/>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="1"/>
+        <v>2822</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="1"/>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="1"/>
+        <v>3074</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="1"/>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="1"/>
+        <v>3326</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="1"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="1"/>
+        <v>3578</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="1"/>
+        <v>3830</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="1"/>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="1"/>
+        <v>4082</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="1"/>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="1"/>
+        <v>4334</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="1"/>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="1"/>
+        <v>4586</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="1"/>
+        <v>462</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="1"/>
+        <v>4838</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="1"/>
+        <v>487</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="1"/>
+        <v>5090</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="1"/>
+        <v>513</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="1"/>
+        <v>5342</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="1"/>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="1"/>
+        <v>5594</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="1"/>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="1"/>
+        <v>5846</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="1"/>
+        <v>588</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="1"/>
+        <v>6098</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="1"/>
+        <v>613</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="1"/>
+        <v>6350</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="1"/>
+        <v>638</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="1"/>
+        <v>6602</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="1"/>
+        <v>663</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="1"/>
+        <v>6854</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="1"/>
+        <v>689</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="1"/>
+        <v>7106</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="1"/>
+        <v>714</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="1"/>
+        <v>7358</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="1"/>
+        <v>739</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="1"/>
+        <v>7610</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="1"/>
+        <v>764</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="1"/>
+        <v>7862</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="1"/>
+        <v>789</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="1"/>
+        <v>8114</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="1"/>
+        <v>814</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="1"/>
+        <v>8366</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="1"/>
+        <v>840</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="1"/>
+        <v>8618</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="1"/>
+        <v>865</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="1"/>
+        <v>8870</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="1"/>
+        <v>890</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="1"/>
+        <v>9122</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="1"/>
+        <v>915</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="1"/>
+        <v>9374</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="1"/>
+        <v>940</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="1"/>
+        <v>9626</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="1"/>
+        <v>965</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="1"/>
+        <v>9878</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <f t="shared" si="1"/>
+        <v>10130</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="1"/>
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <f t="shared" si="1"/>
+        <v>10382</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="1"/>
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <f t="shared" si="1"/>
+        <v>10634</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="1"/>
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <f t="shared" si="1"/>
+        <v>10886</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="1"/>
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <f t="shared" si="1"/>
+        <v>11138</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="1"/>
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <f t="shared" si="1"/>
+        <v>11390</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="1"/>
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <f t="shared" si="1"/>
+        <v>11642</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="1"/>
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <f t="shared" si="1"/>
+        <v>11894</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="1"/>
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <f t="shared" si="1"/>
+        <v>12146</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="1"/>
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <f t="shared" si="1"/>
+        <v>12398</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="1"/>
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <f t="shared" si="1"/>
+        <v>12651</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="1"/>
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <f t="shared" si="1"/>
+        <v>12903</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="1"/>
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="1"/>
+        <v>13155</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="1"/>
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="1"/>
+        <v>13407</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="1"/>
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="1"/>
+        <v>13659</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="1"/>
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="1"/>
+        <v>13911</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="1"/>
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <f t="shared" si="1"/>
+        <v>14163</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="1"/>
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <f t="shared" si="1"/>
+        <v>14415</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="1"/>
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="1"/>
+        <v>14667</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="1"/>
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <f t="shared" si="1"/>
+        <v>14919</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="1"/>
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <f t="shared" si="1"/>
+        <v>15171</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="1"/>
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <f t="shared" si="1"/>
+        <v>15423</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="1"/>
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <f t="shared" si="1"/>
+        <v>15675</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="1"/>
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <f t="shared" si="1"/>
+        <v>15927</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="1"/>
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <f t="shared" si="1"/>
+        <v>16179</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="1"/>
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <f t="shared" si="1"/>
+        <v>16431</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="1"/>
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <f t="shared" ref="A68:A101" si="2">A67+1</f>
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <f t="shared" ref="B68:C100" si="3">INT(B$2 + ($A68 - 1) * ((B$101 - B$2) / 99))</f>
+        <v>16683</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="3"/>
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <f t="shared" si="3"/>
+        <v>16935</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="3"/>
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <f t="shared" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <f t="shared" si="3"/>
+        <v>17187</v>
+      </c>
+      <c r="C70">
+        <f t="shared" si="3"/>
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <f t="shared" si="3"/>
+        <v>17439</v>
+      </c>
+      <c r="C71">
+        <f t="shared" si="3"/>
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <f t="shared" si="3"/>
+        <v>17691</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="3"/>
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <f t="shared" si="3"/>
+        <v>17943</v>
+      </c>
+      <c r="C73">
+        <f t="shared" si="3"/>
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <f t="shared" si="3"/>
+        <v>18195</v>
+      </c>
+      <c r="C74">
+        <f t="shared" si="3"/>
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <f t="shared" si="2"/>
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <f t="shared" si="3"/>
+        <v>18447</v>
+      </c>
+      <c r="C75">
+        <f t="shared" si="3"/>
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <f t="shared" si="3"/>
+        <v>18699</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="3"/>
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <f t="shared" si="3"/>
+        <v>18951</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="3"/>
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <f t="shared" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <f t="shared" si="3"/>
+        <v>19203</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="3"/>
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <f t="shared" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <f t="shared" si="3"/>
+        <v>19455</v>
+      </c>
+      <c r="C79">
+        <f t="shared" si="3"/>
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <f t="shared" si="2"/>
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <f t="shared" si="3"/>
+        <v>19707</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="3"/>
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <f t="shared" si="3"/>
+        <v>19959</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="3"/>
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <f t="shared" si="2"/>
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <f t="shared" si="3"/>
+        <v>20211</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="3"/>
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <f t="shared" si="3"/>
+        <v>20463</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="3"/>
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <f t="shared" si="3"/>
+        <v>20715</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="3"/>
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <f t="shared" si="3"/>
+        <v>20967</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="3"/>
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <f t="shared" si="3"/>
+        <v>21219</v>
+      </c>
+      <c r="C86">
+        <f t="shared" si="3"/>
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <f t="shared" si="2"/>
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <f t="shared" si="3"/>
+        <v>21471</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="3"/>
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <f t="shared" si="3"/>
+        <v>21723</v>
+      </c>
+      <c r="C88">
+        <f t="shared" si="3"/>
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <f t="shared" si="3"/>
+        <v>21975</v>
+      </c>
+      <c r="C89">
+        <f t="shared" si="3"/>
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <f t="shared" si="3"/>
+        <v>22227</v>
+      </c>
+      <c r="C90">
+        <f t="shared" si="3"/>
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <f t="shared" si="3"/>
+        <v>22479</v>
+      </c>
+      <c r="C91">
+        <f t="shared" si="3"/>
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <f t="shared" si="2"/>
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <f t="shared" si="3"/>
+        <v>22731</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="3"/>
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <f t="shared" si="2"/>
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <f t="shared" si="3"/>
+        <v>22983</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="3"/>
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <f t="shared" si="2"/>
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <f t="shared" si="3"/>
+        <v>23235</v>
+      </c>
+      <c r="C94">
+        <f t="shared" si="3"/>
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <f t="shared" si="2"/>
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <f t="shared" si="3"/>
+        <v>23487</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="3"/>
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <f t="shared" si="3"/>
+        <v>23739</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="3"/>
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <f t="shared" si="3"/>
+        <v>23991</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="3"/>
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <f t="shared" si="2"/>
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <f t="shared" si="3"/>
+        <v>24243</v>
+      </c>
+      <c r="C98">
+        <f t="shared" si="3"/>
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <f t="shared" si="2"/>
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <f t="shared" si="3"/>
+        <v>24495</v>
+      </c>
+      <c r="C99">
+        <f t="shared" si="3"/>
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <f t="shared" si="2"/>
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <f t="shared" si="3"/>
+        <v>24747</v>
+      </c>
+      <c r="C100">
+        <f t="shared" si="3"/>
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>25000</v>
+      </c>
+      <c r="C101">
+        <v>2500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CF0CBB-093D-4255-A489-4C757C3F6D8C}">
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>500</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>INT(B$2 + ($A3 - 1) * ((B$101 - B$2) / 99))</f>
+        <v>1505</v>
+      </c>
+      <c r="C3">
+        <f>INT(C$2 + ($A3 - 1) * ((C$101 - C$2) / 99))</f>
+        <v>351</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f t="shared" ref="A4:A67" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ref="B4:C67" si="1">INT(B$2 + ($A4 - 1) * ((B$101 - B$2) / 99))</f>
+        <v>2510</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="1"/>
+        <v>603</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="1"/>
+        <v>3515</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>854</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="1"/>
+        <v>4520</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="1"/>
+        <v>5525</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="1"/>
+        <v>6530</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="1"/>
+        <v>7535</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="1"/>
+        <v>8540</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="1"/>
+        <v>9545</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="1"/>
+        <v>10550</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="1"/>
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="1"/>
+        <v>11555</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="1"/>
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="1"/>
+        <v>12560</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="1"/>
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="1"/>
+        <v>13565</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="1"/>
+        <v>3369</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="1"/>
+        <v>14570</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="1"/>
+        <v>15575</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="1"/>
+        <v>3872</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="1"/>
+        <v>16580</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="1"/>
+        <v>4124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="1"/>
+        <v>17585</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="1"/>
+        <v>4375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="1"/>
+        <v>18590</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="1"/>
+        <v>4627</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="1"/>
+        <v>19595</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="1"/>
+        <v>4878</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="1"/>
+        <v>20601</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="1"/>
+        <v>5130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="1"/>
+        <v>21606</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="1"/>
+        <v>5381</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="1"/>
+        <v>22611</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="1"/>
+        <v>5633</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="1"/>
+        <v>23616</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="1"/>
+        <v>5884</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="1"/>
+        <v>24621</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="1"/>
+        <v>6136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="1"/>
+        <v>25626</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="1"/>
+        <v>6387</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="1"/>
+        <v>26631</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="1"/>
+        <v>6639</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="1"/>
+        <v>27636</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="1"/>
+        <v>6890</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="1"/>
+        <v>28641</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="1"/>
+        <v>7142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="1"/>
+        <v>29646</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="1"/>
+        <v>7393</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="1"/>
+        <v>30651</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="1"/>
+        <v>7645</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="1"/>
+        <v>31656</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="1"/>
+        <v>7896</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="1"/>
+        <v>32661</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="1"/>
+        <v>8148</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="1"/>
+        <v>33666</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="1"/>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="1"/>
+        <v>34671</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="1"/>
+        <v>8651</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="1"/>
+        <v>35676</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="1"/>
+        <v>8903</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="1"/>
+        <v>36681</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="1"/>
+        <v>9154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="1"/>
+        <v>37686</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="1"/>
+        <v>9406</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="1"/>
+        <v>38691</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="1"/>
+        <v>9657</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="1"/>
+        <v>39696</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="1"/>
+        <v>9909</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <f t="shared" si="1"/>
+        <v>40702</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="1"/>
+        <v>10160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <f t="shared" si="1"/>
+        <v>41707</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="1"/>
+        <v>10412</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <f t="shared" si="1"/>
+        <v>42712</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="1"/>
+        <v>10663</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <f t="shared" si="1"/>
+        <v>43717</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="1"/>
+        <v>10915</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <f t="shared" si="1"/>
+        <v>44722</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="1"/>
+        <v>11166</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <f t="shared" si="1"/>
+        <v>45727</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="1"/>
+        <v>11418</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <f t="shared" si="1"/>
+        <v>46732</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="1"/>
+        <v>11669</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <f t="shared" si="1"/>
+        <v>47737</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="1"/>
+        <v>11921</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <f t="shared" si="1"/>
+        <v>48742</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="1"/>
+        <v>12172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <f t="shared" si="1"/>
+        <v>49747</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="1"/>
+        <v>12424</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <f t="shared" si="1"/>
+        <v>50752</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="1"/>
+        <v>12675</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <f t="shared" si="1"/>
+        <v>51757</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="1"/>
+        <v>12927</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="1"/>
+        <v>52762</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="1"/>
+        <v>13178</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="1"/>
+        <v>53767</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="1"/>
+        <v>13430</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="1"/>
+        <v>54772</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="1"/>
+        <v>13681</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="1"/>
+        <v>55777</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="1"/>
+        <v>13933</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <f t="shared" si="1"/>
+        <v>56782</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="1"/>
+        <v>14184</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <f t="shared" si="1"/>
+        <v>57787</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="1"/>
+        <v>14436</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="1"/>
+        <v>58792</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="1"/>
+        <v>14687</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <f t="shared" si="1"/>
+        <v>59797</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="1"/>
+        <v>14939</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <f t="shared" si="1"/>
+        <v>60803</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="1"/>
+        <v>15190</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <f t="shared" si="1"/>
+        <v>61808</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="1"/>
+        <v>15442</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <f t="shared" si="1"/>
+        <v>62813</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="1"/>
+        <v>15693</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <f t="shared" si="1"/>
+        <v>63818</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="1"/>
+        <v>15945</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <f t="shared" si="1"/>
+        <v>64823</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="1"/>
+        <v>16196</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <f t="shared" si="1"/>
+        <v>65828</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="1"/>
+        <v>16448</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <f t="shared" ref="A68:A101" si="2">A67+1</f>
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <f t="shared" ref="B68:C100" si="3">INT(B$2 + ($A68 - 1) * ((B$101 - B$2) / 99))</f>
+        <v>66833</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="3"/>
+        <v>16700</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <f t="shared" si="3"/>
+        <v>67838</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="3"/>
+        <v>16951</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <f t="shared" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <f t="shared" si="3"/>
+        <v>68843</v>
+      </c>
+      <c r="C70">
+        <f t="shared" si="3"/>
+        <v>17203</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <f t="shared" si="3"/>
+        <v>69848</v>
+      </c>
+      <c r="C71">
+        <f t="shared" si="3"/>
+        <v>17454</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <f t="shared" si="3"/>
+        <v>70853</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="3"/>
+        <v>17706</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <f t="shared" si="3"/>
+        <v>71858</v>
+      </c>
+      <c r="C73">
+        <f t="shared" si="3"/>
+        <v>17957</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <f t="shared" si="3"/>
+        <v>72863</v>
+      </c>
+      <c r="C74">
+        <f t="shared" si="3"/>
+        <v>18209</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <f t="shared" si="2"/>
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <f t="shared" si="3"/>
+        <v>73868</v>
+      </c>
+      <c r="C75">
+        <f t="shared" si="3"/>
+        <v>18460</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <f t="shared" si="3"/>
+        <v>74873</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="3"/>
+        <v>18712</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <f t="shared" si="3"/>
+        <v>75878</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="3"/>
+        <v>18963</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <f t="shared" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <f t="shared" si="3"/>
+        <v>76883</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="3"/>
+        <v>19215</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <f t="shared" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <f t="shared" si="3"/>
+        <v>77888</v>
+      </c>
+      <c r="C79">
+        <f t="shared" si="3"/>
+        <v>19466</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <f t="shared" si="2"/>
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <f t="shared" si="3"/>
+        <v>78893</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="3"/>
+        <v>19718</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <f t="shared" si="3"/>
+        <v>79898</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="3"/>
+        <v>19969</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <f t="shared" si="2"/>
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <f t="shared" si="3"/>
+        <v>80904</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="3"/>
+        <v>20221</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <f t="shared" si="3"/>
+        <v>81909</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="3"/>
+        <v>20472</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <f t="shared" si="3"/>
+        <v>82914</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="3"/>
+        <v>20724</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <f t="shared" si="3"/>
+        <v>83919</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="3"/>
+        <v>20975</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <f t="shared" si="3"/>
+        <v>84924</v>
+      </c>
+      <c r="C86">
+        <f t="shared" si="3"/>
+        <v>21227</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <f t="shared" si="2"/>
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <f t="shared" si="3"/>
+        <v>85929</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="3"/>
+        <v>21478</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <f t="shared" si="3"/>
+        <v>86934</v>
+      </c>
+      <c r="C88">
+        <f t="shared" si="3"/>
+        <v>21730</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <f t="shared" si="3"/>
+        <v>87939</v>
+      </c>
+      <c r="C89">
+        <f t="shared" si="3"/>
+        <v>21981</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <f t="shared" si="3"/>
+        <v>88944</v>
+      </c>
+      <c r="C90">
+        <f t="shared" si="3"/>
+        <v>22233</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <f t="shared" si="3"/>
+        <v>89949</v>
+      </c>
+      <c r="C91">
+        <f t="shared" si="3"/>
+        <v>22484</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <f t="shared" si="2"/>
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <f t="shared" si="3"/>
+        <v>90954</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="3"/>
+        <v>22736</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <f t="shared" si="2"/>
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <f t="shared" si="3"/>
+        <v>91959</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="3"/>
+        <v>22987</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <f t="shared" si="2"/>
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <f t="shared" si="3"/>
+        <v>92964</v>
+      </c>
+      <c r="C94">
+        <f t="shared" si="3"/>
+        <v>23239</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <f t="shared" si="2"/>
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <f t="shared" si="3"/>
+        <v>93969</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="3"/>
+        <v>23490</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <f t="shared" si="3"/>
+        <v>94974</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="3"/>
+        <v>23742</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <f t="shared" si="3"/>
+        <v>95979</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="3"/>
+        <v>23993</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <f t="shared" si="2"/>
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <f t="shared" si="3"/>
+        <v>96984</v>
+      </c>
+      <c r="C98">
+        <f t="shared" si="3"/>
+        <v>24245</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <f t="shared" si="2"/>
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <f t="shared" si="3"/>
+        <v>97989</v>
+      </c>
+      <c r="C99">
+        <f t="shared" si="3"/>
+        <v>24496</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <f t="shared" si="2"/>
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <f t="shared" si="3"/>
+        <v>98994</v>
+      </c>
+      <c r="C100">
+        <f t="shared" si="3"/>
+        <v>24748</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>100000</v>
+      </c>
+      <c r="C101">
+        <v>25000</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>